--- a/东方枢纽三方合作计划_明细表.xlsx
+++ b/东方枢纽三方合作计划_明细表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-逐场详细策划" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-报价体系" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-招商引资价值分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-执行机制与保障" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-合作资源与执行机制" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -61,7 +61,7 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00BF9000"/>
+      <color rgb="00B0841A"/>
       <sz val="10"/>
     </font>
     <font>
@@ -73,7 +73,7 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="001F3864"/>
+      <color rgb="002E1F47"/>
       <sz val="12"/>
     </font>
     <font>
@@ -91,12 +91,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="002E1F47"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E5496"/>
+        <fgColor rgb="005B3E8E"/>
       </patternFill>
     </fill>
     <fill>
@@ -106,17 +106,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00F6F3FB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00EAE3F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BF9000"/>
+        <fgColor rgb="00B0841A"/>
       </patternFill>
     </fill>
   </fills>
@@ -179,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -239,12 +239,16 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -627,14 +631,14 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>东方枢纽 × 复旦大学住房政策研究中心 × 杨浦区科技企业联合会  |  下半年 12 场活动总览</t>
+          <t>东方枢纽 × 复旦大学 × 上海市科技企业联合会  |  下半年 12 场活动总览</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>报价单位：人民币·万元（初步建议，最终以指定策划供应商合同为准）</t>
+          <t>以“上海市级 + 浦东新区”资源联动为核心；报价单位：人民币·万元（初步建议，最终以指定策划供应商合同为准）</t>
         </is>
       </c>
     </row>
@@ -715,7 +719,7 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
@@ -744,7 +748,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>浦东新区投资办（浦开大厦 9 楼 200 人厅）</t>
+          <t>浦东新区投资促进中心（浦开大厦 9 楼 200 人厅）</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -753,7 +757,7 @@
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
@@ -791,7 +795,7 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
@@ -820,7 +824,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>浦东新区投资办</t>
+          <t>浦东新区投资促进中心</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
@@ -829,7 +833,7 @@
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
@@ -858,7 +862,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>浦东新区投资办</t>
+          <t>浦东新区投资促进中心</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -867,7 +871,7 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
@@ -905,7 +909,7 @@
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
@@ -943,7 +947,7 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
@@ -972,7 +976,7 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>浦东新区投资办</t>
+          <t>浦东新区投资促进中心</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
@@ -981,7 +985,7 @@
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
@@ -1010,7 +1014,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>浦东新区投资办</t>
+          <t>浦东新区投资促进中心</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1019,7 +1023,7 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
@@ -1057,7 +1061,7 @@
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="14" ht="42" customHeight="1">
@@ -1086,7 +1090,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>国际汇客厅 / 浦东新区投资办</t>
+          <t>国际汇客厅（浦东）/ 浦东新区投资促进中心</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1095,7 +1099,7 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
@@ -1133,7 +1137,7 @@
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -1143,7 +1147,7 @@
         </is>
       </c>
       <c r="H16" s="9" t="n">
-        <v>288</v>
+        <v>111.2</v>
       </c>
     </row>
   </sheetData>
@@ -1229,16 +1233,16 @@
       <c r="C3" s="7" t="inlineStr">
         <is>
           <t>• 解读东方枢纽“进境关外”免税与 180 天停留政策，明确落地路径；
-• 拟出海企业为核心客群，已出海企业提供后市场服务案例；
+• 复旦专家解读出海政策趋势，拟出海企业为核心客群；
 • 首场试点，跑通邀约—注册—跟进—评估全流程。</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>• 浦东新区投资办主任
+          <t>• 市/浦东新区投资促进中心
 • 市商委外办
-• 拟出海/已出海企业决策层
-• 联合会社群精选企业</t>
+• 复旦相关专家
+• 拟出海/已出海企业决策层</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
@@ -1248,7 +1252,7 @@
         </is>
       </c>
       <c r="F3" s="11" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="4" ht="120" customHeight="1">
@@ -1260,14 +1264,14 @@
           <t>绿色能源与新兴储能出海专场
 ⏰ 7 月底（约 7/30）
 👥 市区专场 · 80 人
-📍 浦东新区投资办（浦开大厦 9 楼 200 人厅）</t>
+📍 浦东新区投资促进中心（浦开大厦 9 楼 200 人厅）</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>• 聚焦新能源汽车、充电桩、锂电与新兴储能出海东南亚；
 • 对标已签约的江苏协鑫，邀请特斯拉、比亚迪、特来电、宁德时代等；
-• 延伸低空经济（如沃兰特 eVTOL，锂电池关联）作为新兴话题。</t>
+• 延伸低空经济（如沃兰特 eVTOL，锂电池关联）作为新兴科技话题。</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1286,7 +1290,7 @@
         </is>
       </c>
       <c r="F4" s="13" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" ht="120" customHeight="1">
@@ -1304,7 +1308,7 @@
       <c r="C5" s="7" t="inlineStr">
         <is>
           <t>• 借上海 76 个领事馆领事集中参加年会之机集中邀约；
-• 联动杨浦、闵行、浦东挂牌“国际汇客厅”，配套东南亚特色餐饮；
+• 联动浦东/闵行挂牌“国际汇客厅”，配套东南亚特色餐饮；
 • 主论坛 + 分行业对接，作为全年引流总入口（10% 导流即达标）。</t>
         </is>
       </c>
@@ -1323,7 +1327,7 @@
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="120" customHeight="1">
@@ -1335,7 +1339,7 @@
           <t>长三角属地（市级）商会对接会
 ⏰ 8 月底（约 8/27）
 👥 市区专场 · 80 人
-📍 浦东新区投资办</t>
+📍 浦东新区投资促进中心</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1359,7 +1363,7 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="7" ht="120" customHeight="1">
@@ -1371,7 +1375,7 @@
           <t>新型国际贸易与跨境服务专场
 ⏰ 9 月中旬（约 9/10）
 👥 市区专场 · 80 人
-📍 浦东新区投资办</t>
+📍 浦东新区投资促进中心</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
@@ -1395,7 +1399,7 @@
         </is>
       </c>
       <c r="F7" s="11" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="8" ht="120" customHeight="1">
@@ -1413,13 +1417,13 @@
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>• 依托浦东机场/枢纽区位，聚焦临空经济与航空供应链；
-• 对接双飞及其供应链企业，探讨维修、配送、保税协同；
+• 对接航空及其供应链企业，探讨维修、配送、保税协同；
 • 闭门深度对接，锁定高价值供应链租户。</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>• 双飞及供应链企业
+          <t>• 航空及供应链企业
 • 航空维修/物流企业
 • 临空经济服务商</t>
         </is>
@@ -1431,7 +1435,7 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="9" ht="120" customHeight="1">
@@ -1450,7 +1454,7 @@
         <is>
           <t>• 推动地级市政府在枢纽设“招商飞地/办事处”，走港口出海；
 • 对接内陆无出海口城市的差异化需求（华东/华中/中原）；
-• 由管委会领导、分管副市长出席背书。</t>
+• 由市/区投资促进部门与片区管委会领导出席背书。</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -1458,7 +1462,7 @@
           <t>• 浙江温岭/湖州
 • 山东德州/临沂
 • 广州（白云贸易街区）
-• 枢纽管委会领导</t>
+• 片区管委会领导</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -1468,7 +1472,7 @@
         </is>
       </c>
       <c r="F9" s="11" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="10" ht="120" customHeight="1">
@@ -1480,21 +1484,22 @@
           <t>工业互联网与数据中心（算力出海）专场
 ⏰ 10 月底（约 10/29）
 👥 市区专场 · 80 人
-📍 浦东新区投资办</t>
+📍 浦东新区投资促进中心</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
           <t>• 依托枢纽数据中心与全网通，主打境外算力低成本接入；
 • 面向工业互联网、AI/算力、跨境 SaaS 企业；
-• 以“境外可用、算力便宜”为差异化卖点。</t>
+• 联合复旦科技智库解读产业趋势，以“境外可用、算力便宜”为卖点。</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
           <t>• 数据中心/算力企业
 • 工业互联网平台
-• 跨境 SaaS / AI 企业</t>
+• 跨境 SaaS / AI 企业
+• 复旦科技专家</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1504,7 +1509,7 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="11" ht="120" customHeight="1">
@@ -1516,7 +1521,7 @@
           <t>生物医药 · 药械贸易出海专场
 ⏰ 11 月中旬（约 11/12）
 👥 市区专场 · 80 人
-📍 浦东新区投资办</t>
+📍 浦东新区投资促进中心</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
@@ -1540,7 +1545,7 @@
         </is>
       </c>
       <c r="F11" s="11" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="12" ht="120" customHeight="1">
@@ -1576,7 +1581,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="13" ht="120" customHeight="1">
@@ -1588,12 +1593,12 @@
           <t>高端服务业 · 国际汇客厅资源对接
 ⏰ 12 月上旬（约 12/10）
 👥 市区专场 · 80 人
-📍 国际汇客厅 / 浦东新区投资办</t>
+📍 国际汇客厅（浦东）/ 浦东新区投资促进中心</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>• 联动瑞典/北欧创新国际中心等国际汇客厅资源；
+          <t>• 联动浦东挂牌的国际汇客厅（瑞典/北欧创新中心等）资源；
 • 撮合外资机构与高端服务企业落地关外；
 • 以国际化服务生态提升项目品牌能级。</t>
         </is>
@@ -1612,7 +1617,7 @@
         </is>
       </c>
       <c r="F13" s="11" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="14" ht="120" customHeight="1">
@@ -1630,15 +1635,15 @@
       <c r="C14" s="5" t="inlineStr">
         <is>
           <t>• 面向全年沉淀的、对东方枢纽明确感兴趣的企业二次跟进；
-• 管委会局长（张希）、分管副市长、集团副总裁出席，年度成果发布；
+• 市/区商务委与投资促进部门、片区管委会领导出席，年度成果发布；
 • 现场集中签约/意向落地，形成闭环收官。</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>• 枢纽管委会领导
-• 分管副市长
-• 集团副总裁
+          <t>• 市/区商务委与投资促进部门
+• 片区管委会领导
+• 复旦及联合会代表
 • 全年意向企业 60-70 家</t>
         </is>
       </c>
@@ -1649,7 +1654,7 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1668,7 +1673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1720,13 +1725,13 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="5">
@@ -1736,13 +1741,13 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="C5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>5</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -1752,13 +1757,13 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
@@ -1768,13 +1773,13 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="D7" s="6" t="n">
         <v>2.5</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1784,13 +1789,13 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -1800,13 +1805,13 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="D9" s="6" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -1816,13 +1821,13 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1832,13 +1837,13 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -1880,10 +1885,10 @@
         <v>4</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>9.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>39.2</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="16">
@@ -1896,10 +1901,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>22.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>136.8</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="17">
@@ -1912,10 +1917,10 @@
         <v>2</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>112</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18">
@@ -1933,13 +1938,21 @@
         </is>
       </c>
       <c r="D18" s="19" t="n">
-        <v>288</v>
+        <v>111.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>说明：按东方枢纽标准优化后，全年合计约 111.2 万元，较初版 288.0 万元下调约 61%；上不封顶原则下的合理基准价，可按规模/邀约确认后微调。</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A20:D20"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -2177,7 +2190,7 @@
           <t>说明</t>
         </is>
       </c>
-      <c r="C18" s="21" t="n"/>
+      <c r="C18" s="22" t="n"/>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="14" t="inlineStr">
@@ -2218,12 +2231,12 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>品牌能级跃升</t>
+          <t>市区联动背书</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>复旦学术背书 + 联合会近 2 万企业社群 + 国企/政府背书，提升项目对外话语权与租金议价能力。</t>
+          <t>市级平台 + 浦东新区落地 + 复旦学术/科技智库背书，提升项目对外话语权与租金议价能力。</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2282,7 @@
           <t>数值</t>
         </is>
       </c>
-      <c r="C27" s="21" t="n"/>
+      <c r="C27" s="22" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
@@ -2277,9 +2290,9 @@
           <t>全年活动投入（12 场）</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
-        <is>
-          <t>约 288 万元</t>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>约 111.2 万元</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2302,7 @@
           <t>累计触达企业决策层</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>约 1,000 家 / 人次</t>
         </is>
@@ -2301,7 +2314,7 @@
           <t>预计落地/签约企业</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>约 21 家 + 5–8 个政府飞地</t>
         </is>
@@ -2313,7 +2326,7 @@
           <t>中性情景带动去化</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>约 6.65 万方（≈ 133 万方的 5%）</t>
         </is>
@@ -2322,12 +2335,12 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>社群存量导流池</t>
-        </is>
-      </c>
-      <c r="B32" s="22" t="inlineStr">
-        <is>
-          <t>近 2 万家科技企业（年底目标）</t>
+          <t>单位去化获客成本</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>约 1.67 万元 / 万方（中性情景）</t>
         </is>
       </c>
     </row>
@@ -2361,99 +2374,211 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>执行机制与合规保障</t>
+          <t>合作资源背书与执行机制</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>一、三方合作定位</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>复旦大学
+（学术与科技智库）</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>依托复旦大学住房政策研究中心及科技成果转化、产业研究资源；提供政策研究、课题背书、复旦专家智库与学术公信力，为项目注入“科创 + 学术”双重能级。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>上海市科技企业联合会
+（科技产业组织）</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>市级科技企业组织，覆盖上海及长三角科技企业社群资源；负责科技企业精准邀约、科创内容策划、活动执行、社群传播与会后跟进评估。（备选/补充科技组织：上海市科学技术协会、上海市软件和信息服务业行业协会等）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>东方枢纽
+（招商主体）</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>133 万方招商引资项目，含浦东机场、毗邻高铁站，具备“进境关外”免税/停留政策优势；聚焦六大核心产业招商，联动市级与浦东新区商务、投资促进资源，提供政府背书、场地资源与指定策划供应商通道。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>备选/补充科技组织</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>上海市科学技术协会、上海市软件和信息服务业行业协会、上海市生物医药行业协会、长三角科技型企业创新联盟</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>二、政府资源背书矩阵（市级 + 浦东新区联动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>上海市级资源</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>• 上海市商务委员会
+• 上海市投资促进服务中心
+• 上海市商务委外事办公室（领事馆/国际资源对接）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>浦东新区资源</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>• 浦东新区商务委员会
+• 浦东新区投资促进中心（浦开大厦九楼 200 人会议场地）
+• 浦东新区分管领导及片区管委会</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>联动逻辑</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>“1 + 1”市区联动：以市级平台提升能级与权威性，以浦东新区落地承接与就近服务。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
+        <is>
+          <t>三、执行机制与合规保障</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>环节</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>要点</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>邀约与名单</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>活动前提供邀约名单、参会人数、人员背景，供东方枢纽走 OA 流程。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>预算与付款</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>预算随案提交；经费经东方枢纽指定策划供应商签约支付。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>场地与搭建</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>由持国货区通行证的指定供应商完成搭建，外部团队协同会务邀约衍生服务。</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>数据与跟进</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>注册数据后台全量录入，导入 CRM/名录，支撑会后评估报告。</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>节奏与灵活度</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>两周一场（小而美）或一月一场（大型）；资源成熟可提档，档期可调。</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>质量把控</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>嘉宾须为决策层，重质量而非排面，保障长期可持续合作。</t>
         </is>

--- a/东方枢纽三方合作计划_明细表.xlsx
+++ b/东方枢纽三方合作计划_明细表.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-逐场详细策划" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-报价体系" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-招商引资价值分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-合作资源与执行机制" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-招商标的与执行机制" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -766,12 +766,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>8 月 18 日（已定）</t>
+          <t>8 月 18 日前后</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>东南亚出海高峰论坛（旗舰）</t>
+          <t>东南亚出海精选对接闭门会（借 8/18 大会引流）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -781,21 +781,21 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>大型论坛 · 200 人</t>
+          <t>小而美闭门 · 30 人</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>经贸大厦 86 楼</t>
+          <t>东方枢纽园区（浦开大厦 9 楼）</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>22</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>东方枢纽全产业链招商年度峰会暨签约（旗舰收官）</t>
+          <t>A 片区全产业链招商闭门对接（年度收官）</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -1123,21 +1123,21 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>大型峰会 · 200 人</t>
+          <t>小而美闭门 · 30 人</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>经贸大厦 86 楼 / 枢纽</t>
+          <t>东方枢纽园区</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>22</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="16">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="H16" s="9" t="n">
-        <v>111.2</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1299,35 +1299,34 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>东南亚出海高峰论坛（旗舰）
-⏰ 8 月 18 日（已定）
-👥 大型论坛 · 200 人
-📍 经贸大厦 86 楼</t>
+          <t>东南亚出海精选对接闭门会（借 8/18 大会引流）
+⏰ 8 月 18 日前后
+👥 小而美闭门 · 30 人
+📍 东方枢纽园区（浦开大厦 9 楼）</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>• 借上海 76 个领事馆领事集中参加年会之机集中邀约；
-• 联动浦东/闵行挂牌“国际汇客厅”，配套东南亚特色餐饮；
-• 主论坛 + 分行业对接，作为全年引流总入口（10% 导流即达标）。</t>
+          <t>• 借 8/18 领事馆年会大流量，精选 ~10% 高质量出海企业过来做小范围对接；
+• 小而美闭门形式，配套东南亚特色茶歇，聚焦深度撮合；
+• 邀请少数领事/外办代表点睛，重质量不求排面。</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>• 东南亚各国领事
-• 市商委外办主任
-• 国际汇客厅合作方
-• 六大产业出海企业</t>
+          <t>• 东南亚重点国家领事（精选）
+• 市商委外办代表
+• 六大产业出海企业决策层</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>• 年度最大流量锚点，为后续专场输送高质量线索；
-• 以国际资源提升项目国际能级，吸引外资落“进境关外”。</t>
+          <t>• 以低成本承接大会溢出流量，转化为 A 片区精准线索；
+• 国际资源点睛提升项目国际能级，吸引外资落“进境关外”。</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
-        <v>22</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="6" ht="120" customHeight="1">
@@ -1626,35 +1625,34 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>东方枢纽全产业链招商年度峰会暨签约（旗舰收官）
+          <t>A 片区全产业链招商闭门对接（年度收官）
 ⏰ 12 月中旬（约 12/17）
-👥 大型峰会 · 200 人
-📍 经贸大厦 86 楼 / 枢纽</t>
+👥 小而美闭门 · 30 人
+📍 东方枢纽园区</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>• 面向全年沉淀的、对东方枢纽明确感兴趣的企业二次跟进；
-• 市/区商务委与投资促进部门、片区管委会领导出席，年度成果发布；
-• 现场集中签约/意向落地，形成闭环收官。</t>
+          <t>• 面向全年沉淀的、对 A 片区办公明确感兴趣的企业做二次跟进；
+• 小范围闭门对接 + 意向企业现场看盘选址（结合 A 片区产品）；
+• 片区管委会领导出席点睛，形成年度闭环收官。</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>• 市/区商务委与投资促进部门
-• 片区管委会领导
+          <t>• 片区管委会/投资促进部门代表
 • 复旦及联合会代表
-• 全年意向企业 60-70 家</t>
+• 全年意向企业（精选 30 家内）</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>• 全年线索集中转化，签约仪式放大招商声量；
-• 沉淀年度招商白皮书，支撑来年持续合作。</t>
+          <t>• 全年线索集中转化，直接对接 A 片区办公产品选址；
+• 沉淀年度招商小结，支撑来年持续合作。</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>22</v>
+        <v>3.6</v>
       </c>
     </row>
   </sheetData>
@@ -1882,13 +1880,13 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>3.6</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>14.4</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="16">
@@ -1914,13 +1912,13 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>22</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1938,13 +1936,13 @@
         </is>
       </c>
       <c r="D18" s="19" t="n">
-        <v>111.2</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="21" t="inlineStr">
         <is>
-          <t>说明：按东方枢纽标准优化后，全年合计约 111.2 万元，较初版 288.0 万元下调约 61%；上不封顶原则下的合理基准价，可按规模/邀约确认后微调。</t>
+          <t>说明：按东方枢纽标准优化后，全年合计约 74.4 万元，较初版 288.0 万元下调约 74%；上不封顶原则下的合理基准价，可按规模/邀约确认后微调。</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1975,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>招商引资价值分析 · 针对东方枢纽 133 万方项目</t>
+          <t>招商引资价值分析 · 针对东方枢纽 A 片区办公项目（约 30 万㎡）</t>
         </is>
       </c>
     </row>
@@ -2020,12 +2018,12 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>2 场×200 + 6 场×80 + 4 场×30</t>
+          <t>6 场×80 + 6 场×30</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>660</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2040,7 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>约 200 家</t>
+          <t>约 132 家</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2057,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>约 70 家</t>
+          <t>约 46 家</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2074,7 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>约 21 家</t>
+          <t>约 14 家</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2098,7 @@
     <row r="11">
       <c r="A11" s="17" t="inlineStr">
         <is>
-          <t>二、去化面积测算（133 万方 × 情景去化率）</t>
+          <t>二、去化面积测算（A 片区办公约 30 万㎡ × 情景去化率）</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2132,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>约 3.99 万方</t>
+          <t>约 0.9 万㎡</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2149,7 @@
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>约 6.65 万方</t>
+          <t>约 1.5 万㎡</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2166,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>约 10.64 万方</t>
+          <t>约 2.4 万㎡</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2198,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>12 场围绕六大产业定向邀约，累计触达约 1,000 家企业决策层，较泛化招商大幅提升线索质量与转化效率。</t>
+          <t>12 场围绕六大产业定向邀约，累计触达约 660 家企业决策层，较泛化招商大幅提升线索质量与转化效率。</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2210,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>“论坛引流→专场深挖→闭门对接→签约落地”漏斗清晰，中性情景可带动约 6.65 万方去化（占 133 万方约 5%）。</t>
+          <t>“大会引流→专场深挖→闭门对接→选址落地”漏斗清晰，中性情景可带动约 1.5 万㎡ 去化（占 A 片区办公约 30 万㎡ 的 5%）。</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2290,7 @@
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>约 111.2 万元</t>
+          <t>约 74.4 万元</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2302,7 @@
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>约 1,000 家 / 人次</t>
+          <t>约 660 家 / 人次</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2314,7 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>约 21 家 + 5–8 个政府飞地</t>
+          <t>约 14 家 + 5–8 个政府飞地</t>
         </is>
       </c>
     </row>
@@ -2328,19 +2326,19 @@
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>约 6.65 万方（≈ 133 万方的 5%）</t>
+          <t>约 1.5 万㎡（≈ A 片区办公 30 万㎡ 的 5%）</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>单位去化获客成本</t>
+          <t>单位落地企业获客成本</t>
         </is>
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>约 1.67 万元 / 万方（中性情景）</t>
+          <t>约 5.3 万元 / 家（中性情景）</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2384,82 +2382,154 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>合作资源背书与执行机制</t>
+          <t>招商标的 · 合作资源背书 · 执行机制</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
+          <t>〇、招商标的：东方枢纽集团 A 片区整体办公项目</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>项目定位</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>隶属浦东国际航空城规划，主打“枢纽 + 办公”复合业态；紧邻浦东机场/高铁，具备“进境关外”免税/停留政策优势。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>体量规模</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>办公产品建筑面积约 30 万㎡（汇总自 A 片区产品布局，最终以官方口径为准）（说明：招商标的为 A 片区办公项目，非“133 万方”）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>四大产品线</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>• 国际商务独栋：花园独栋 + 独立庭院、私享屋顶飞机观景露台、枢纽 0 距离、抗震隔音、企业 LOGO 多维展示
+• 枢纽办公 · 国际 A+ 级：站前中枢、极致动线、双首层活力交互、灵活共享办公、黄金区位企业展厅（A1A-01/A3-01/A4B-01）
+• 国际总部 · 国际 A+ 级：三叠拼特色办公、空中花园、智慧泊车、智慧门禁及梯控、中庭共栖广场
+• 品质标办 · A+ 级：垂直绿化、私享露台与公共花园、空中绿廊、生态社交空间、绿色三星认证</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="66" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>销售/租赁模式</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>• 销售 / 租赁并重：北/南上盖及多栋采用“分层销售 + 整层/单元/分时租赁”组合；
+• 灵活门槛：多栋支持按 300 ㎡ 最小单元分割出租，单层约 1600–6000 ㎡；
+• 地块标识：A1A-01/A3-01/A4B-01 核心枢纽办公，N 系（N3–N7）北上盖、S 系（S3/S4）南上盖。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>活动↔产品匹配</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>活动导流企业按需匹配：出海/贸易企业→枢纽办公·品质标办（300 ㎡ 起分割出租）；总部型企业→国际总部/国际商务独栋；政府飞地→小面积单元办事处。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
           <t>一、三方合作定位</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>复旦大学
 （学术与科技智库）</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>依托复旦大学住房政策研究中心及科技成果转化、产业研究资源；提供政策研究、课题背书、复旦专家智库与学术公信力，为项目注入“科创 + 学术”双重能级。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>上海市科技企业联合会
 （科技产业组织）</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>市级科技企业组织，覆盖上海及长三角科技企业社群资源；负责科技企业精准邀约、科创内容策划、活动执行、社群传播与会后跟进评估。（备选/补充科技组织：上海市科学技术协会、上海市软件和信息服务业行业协会等）</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>东方枢纽
 （招商主体）</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>133 万方招商引资项目，含浦东机场、毗邻高铁站，具备“进境关外”免税/停留政策优势；聚焦六大核心产业招商，联动市级与浦东新区商务、投资促进资源，提供政府背书、场地资源与指定策划供应商通道。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>东方枢纽集团 A 片区整体办公招商项目（隶属浦东国际航空城规划），含浦东机场、毗邻高铁站，具备“进境关外”免税/停留政策优势；聚焦六大核心产业招商，联动市级与浦东新区商务、投资促进资源，提供政府背书、场地与指定供应商通道。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>备选/补充科技组织</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>上海市科学技术协会、上海市软件和信息服务业行业协会、上海市生物医药行业协会、长三角科技型企业创新联盟</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>二、政府资源背书矩阵（市级 + 浦东新区联动）</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>上海市级资源</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>• 上海市商务委员会
 • 上海市投资促进服务中心
@@ -2467,13 +2537,13 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>浦东新区资源</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>• 浦东新区商务委员会
 • 浦东新区投资促进中心（浦开大厦九楼 200 人会议场地）
@@ -2481,104 +2551,104 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>联动逻辑</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>“1 + 1”市区联动：以市级平台提升能级与权威性，以浦东新区落地承接与就近服务。</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>三、执行机制与合规保障</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>环节</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>要点</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>邀约与名单</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>活动前提供邀约名单、参会人数、人员背景，供东方枢纽走 OA 流程。</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>预算与付款</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>预算随案提交；经费经东方枢纽指定策划供应商签约支付。</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>场地与搭建</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>由持国货区通行证的指定供应商完成搭建，外部团队协同会务邀约衍生服务。</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>数据与跟进</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>注册数据后台全量录入，导入 CRM/名录，支撑会后评估报告。</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>节奏与灵活度</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>两周一场（小而美）或一月一场（大型）；资源成熟可提档，档期可调。</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>质量把控</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>嘉宾须为决策层，重质量而非排面，保障长期可持续合作。</t>
         </is>
